--- a/data/Pick_Calibration.xlsx
+++ b/data/Pick_Calibration.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-23 ~ 2026-08-19</t>
+          <t>2026-07-23 ~ 2026-08-20</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3,357건</t>
+          <t>3,468건</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>689건</t>
+          <t>713건</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.5%</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.2351</t>
+          <t>0.2345</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>40.7%</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.1%</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-4.0% ~ +3.2%</t>
+          <t>-3.9% ~ +3.1%</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.8%</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-6.1%</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-9.8% ~ -2.6%</t>
+          <t>-9.7% ~ -2.6%</t>
         </is>
       </c>
     </row>
@@ -716,21 +716,21 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>500</v>
+        <v>518</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+3.3%</t>
+          <t>+3.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -744,25 +744,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>947</v>
+        <v>982</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+1.4%</t>
+          <t>+1.2%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="4">
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>764</v>
+        <v>788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -781,12 +781,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+1.8%</t>
+          <t>+1.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>662</v>
+        <v>678</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -809,12 +809,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -837,12 +837,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -940,11 +940,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1121</v>
+        <v>1160</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>781</v>
+        <v>807</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>754</v>
+        <v>780</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>701</v>
+        <v>721</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2328</v>
+        <v>2439</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1160,11 +1160,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.2329</v>
+        <v>0.2321</v>
       </c>
     </row>
     <row r="3">

--- a/data/Pick_Calibration.xlsx
+++ b/data/Pick_Calibration.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-23 ~ 2026-08-20</t>
+          <t>2026-07-23 ~ 2026-08-21</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3,468건</t>
+          <t>3,747건</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>713건</t>
+          <t>765건</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.2345</t>
+          <t>0.2339</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.2466</t>
+          <t>0.2465</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.9%</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>41.0%</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-3.9% ~ +3.1%</t>
+          <t>-3.5% ~ +3.4%</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-5.9%</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-9.7% ~ -2.6%</t>
+          <t>-9.2% ~ -2.4%</t>
         </is>
       </c>
     </row>
@@ -716,21 +716,21 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>518</v>
+        <v>565</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+3.2%</t>
+          <t>+2.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>982</v>
+        <v>1049</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -753,12 +753,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>+1.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>788</v>
+        <v>862</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -781,12 +781,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+1.6%</t>
+          <t>+1.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -800,21 +800,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>678</v>
+        <v>723</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>280</v>
+        <v>309</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -837,16 +837,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="7">
@@ -856,21 +856,21 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1160</v>
+        <v>1253</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -954,17 +954,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>807</v>
+        <v>869</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1020,11 +1020,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>780</v>
+        <v>842</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>721</v>
+        <v>783</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-6.7%</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2439</v>
+        <v>2520</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.2321</v>
+        <v>0.2322</v>
       </c>
     </row>
     <row r="3">
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>815</v>
+        <v>1013</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1183,16 +1183,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.2416</v>
+        <v>0.2377</v>
       </c>
     </row>
     <row r="4">

--- a/data/Pick_Calibration.xlsx
+++ b/data/Pick_Calibration.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3,747건</t>
+          <t>3,837건</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>765건</t>
+          <t>779건</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>+0.4%</t>
+          <t>+0.5%</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.2339</t>
+          <t>0.2337</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>41.1%</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>+0.1%</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-3.5% ~ +3.4%</t>
+          <t>-3.2% ~ +3.5%</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.7%</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-5.6%</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-9.2% ~ -2.4%</t>
+          <t>-8.9% ~ -2.3%</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>565</v>
+        <v>580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -725,12 +725,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+2.9%</t>
+          <t>+2.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1049</v>
+        <v>1068</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -753,12 +753,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+1.3%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>862</v>
+        <v>889</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -800,21 +800,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>723</v>
+        <v>741</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -837,12 +837,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1253</v>
+        <v>1283</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.4%</t>
         </is>
       </c>
     </row>
@@ -980,11 +980,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>869</v>
+        <v>889</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>842</v>
+        <v>862</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>783</v>
+        <v>803</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.8%</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1013</v>
+        <v>1103</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1183,16 +1183,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.2377</v>
+        <v>0.2367</v>
       </c>
     </row>
     <row r="4">

--- a/data/Pick_Calibration.xlsx
+++ b/data/Pick_Calibration.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-23 ~ 2026-08-21</t>
+          <t>2026-07-23 ~ 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3,837건</t>
+          <t>4,022건</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>779건</t>
+          <t>813건</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.2337</t>
+          <t>0.2333</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>41.0%</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>40.9%</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-3.2% ~ +3.5%</t>
+          <t>-3.2% ~ +3.3%</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.6%</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.7%</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-8.9% ~ -2.3%</t>
+          <t>-9.0% ~ -2.4%</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>580</v>
+        <v>607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -725,16 +725,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+2.8%</t>
+          <t>+3.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="3">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1068</v>
+        <v>1122</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>889</v>
+        <v>935</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -781,12 +781,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+1.0%</t>
+          <t>+0.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>741</v>
+        <v>768</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -809,16 +809,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="6">
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -837,16 +837,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="7">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1283</v>
+        <v>1346</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>889</v>
+        <v>931</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-7.1%</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>862</v>
+        <v>904</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>803</v>
+        <v>841</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2520</v>
+        <v>2651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.2322</v>
+        <v>0.2315</v>
       </c>
     </row>
     <row r="3">
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1103</v>
+        <v>1157</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.2367</v>
+        <v>0.2371</v>
       </c>
     </row>
     <row r="4">

--- a/data/Pick_Calibration.xlsx
+++ b/data/Pick_Calibration.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-23 ~ 2026-08-23</t>
+          <t>2026-07-23 ~ 2026-08-24</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4,022건</t>
+          <t>4,383건</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>813건</t>
+          <t>882건</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>+0.4%</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.2333</t>
+          <t>0.2328</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>40.6%</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>-0.6%</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-3.2% ~ +3.3%</t>
+          <t>-3.7% ~ +2.6%</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-6.2%</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-9.0% ~ -2.4%</t>
+          <t>-9.4% ~ -3.1%</t>
         </is>
       </c>
     </row>
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>607</v>
+        <v>648</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+3.0%</t>
+          <t>+3.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="3">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1122</v>
+        <v>1245</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -753,12 +753,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>+0.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -772,21 +772,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>935</v>
+        <v>1014</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>+0.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -800,21 +800,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>768</v>
+        <v>829</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -828,21 +828,21 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>337</v>
+        <v>372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1346</v>
+        <v>1469</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>931</v>
+        <v>1013</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -989,12 +989,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>904</v>
+        <v>986</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1060,11 +1060,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>841</v>
+        <v>915</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2651</v>
+        <v>2913</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.2315</v>
+        <v>0.2313</v>
       </c>
     </row>
     <row r="3">
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1157</v>
+        <v>1256</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.2371</v>
+        <v>0.236</v>
       </c>
     </row>
     <row r="4">

--- a/data/Pick_Calibration.xlsx
+++ b/data/Pick_Calibration.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-23 ~ 2026-08-24</t>
+          <t>2026-07-23 ~ 2026-08-25</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4,383건</t>
+          <t>4,469건</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>882건</t>
+          <t>894건</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.2328</t>
+          <t>0.2327</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.8%</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>40.5%</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-3.7% ~ +2.6%</t>
+          <t>-3.9% ~ +2.4%</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-6.4%</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-9.4% ~ -3.1%</t>
+          <t>-9.6% ~ -3.3%</t>
         </is>
       </c>
     </row>
@@ -716,21 +716,21 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>648</v>
+        <v>661</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+3.1%</t>
+          <t>+2.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1245</v>
+        <v>1270</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -753,12 +753,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+0.9%</t>
+          <t>+1.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1014</v>
+        <v>1034</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+0.4%</t>
+          <t>+0.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>829</v>
+        <v>844</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -837,12 +837,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -856,21 +856,21 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1469</v>
+        <v>1499</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1013</v>
+        <v>1033</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>986</v>
+        <v>1006</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-6.7%</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>915</v>
+        <v>931</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2913</v>
+        <v>2999</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.2313</v>
+        <v>0.2311</v>
       </c>
     </row>
     <row r="3">

--- a/data/Pick_Calibration.xlsx
+++ b/data/Pick_Calibration.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-23 ~ 2026-08-25</t>
+          <t>2026-07-23 ~ 2026-08-26</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4,469건</t>
+          <t>4,697건</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>894건</t>
+          <t>927건</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.2327</t>
+          <t>0.2323</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.5%</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.6%</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-1.1%</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-3.9% ~ +2.4%</t>
+          <t>-4.1% ~ +2.0%</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-6.7%</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-9.6% ~ -3.3%</t>
+          <t>-9.8% ~ -3.7%</t>
         </is>
       </c>
     </row>
@@ -716,21 +716,21 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>661</v>
+        <v>696</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+2.8%</t>
+          <t>+2.7%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1270</v>
+        <v>1334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -753,12 +753,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+1.0%</t>
+          <t>+1.2%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1034</v>
+        <v>1084</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -781,12 +781,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>844</v>
+        <v>885</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -837,12 +837,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1499</v>
+        <v>1577</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -980,11 +980,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1033</v>
+        <v>1085</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1006</v>
+        <v>1058</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>931</v>
+        <v>977</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,27 +1069,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>49.6%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>49.7%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>49.7%</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-6.9%</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2999</v>
+        <v>3128</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1160,11 +1160,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.2311</v>
+        <v>0.2309</v>
       </c>
     </row>
     <row r="3">
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1256</v>
+        <v>1355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1183,16 +1183,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.236</v>
+        <v>0.2351</v>
       </c>
     </row>
     <row r="4">

--- a/data/Pick_Calibration.xlsx
+++ b/data/Pick_Calibration.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4,697건</t>
+          <t>4,796건</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>927건</t>
+          <t>944건</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.2323</t>
+          <t>0.2324</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>40.4%</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-0.9%</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-4.1% ~ +2.0%</t>
+          <t>-3.9% ~ +2.1%</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.6%</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-9.8% ~ -3.7%</t>
+          <t>-9.6% ~ -3.5%</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>696</v>
+        <v>712</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -725,16 +725,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+2.7%</t>
+          <t>+2.6%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="3">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1334</v>
+        <v>1352</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1084</v>
+        <v>1114</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -781,12 +781,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>+0.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>885</v>
+        <v>909</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="6">
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -837,12 +837,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1577</v>
+        <v>1610</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1085</v>
+        <v>1107</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1058</v>
+        <v>1080</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>977</v>
+        <v>999</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1174,11 +1174,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1355</v>
+        <v>1454</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">

--- a/data/Pick_Calibration.xlsx
+++ b/data/Pick_Calibration.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-23 ~ 2026-08-26</t>
+          <t>2026-07-23 ~ 2026-08-27</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4,796건</t>
+          <t>5,010건</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>944건</t>
+          <t>979건</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.4%</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.0%</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-3.9% ~ +2.1%</t>
+          <t>-3.9% ~ +2.0%</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.0%</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-9.6% ~ -3.5%</t>
+          <t>-9.5% ~ -3.6%</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>712</v>
+        <v>745</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -725,12 +725,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+2.6%</t>
+          <t>+2.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1352</v>
+        <v>1405</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>+1.2%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1114</v>
+        <v>1171</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>909</v>
+        <v>948</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -809,12 +809,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -837,12 +837,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1610</v>
+        <v>1682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1107</v>
+        <v>1155</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1080</v>
+        <v>1128</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1060,16 +1060,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>999</v>
+        <v>1045</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3128</v>
+        <v>3261</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.2309</v>
+        <v>0.2315</v>
       </c>
     </row>
     <row r="3">
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1454</v>
+        <v>1535</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.2351</v>
+        <v>0.2338</v>
       </c>
     </row>
     <row r="4">

--- a/data/Pick_Calibration.xlsx
+++ b/data/Pick_Calibration.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-23 ~ 2026-08-27</t>
+          <t>2026-07-23 ~ 2026-08-28</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5,010건</t>
+          <t>5,109건</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>979건</t>
+          <t>995건</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.2324</t>
+          <t>0.2323</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.2%</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.3%</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.1%</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-3.9% ~ +2.0%</t>
+          <t>-4.1% ~ +1.9%</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-6.8%</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-9.5% ~ -3.6%</t>
+          <t>-9.7% ~ -3.7%</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>745</v>
+        <v>761</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -725,16 +725,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+2.3%</t>
+          <t>+2.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="3">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1405</v>
+        <v>1428</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,21 +772,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1171</v>
+        <v>1197</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>948</v>
+        <v>969</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -809,12 +809,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1682</v>
+        <v>1715</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1155</v>
+        <v>1177</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1020,11 +1020,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1128</v>
+        <v>1150</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1045</v>
+        <v>1067</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3261</v>
+        <v>3306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1535</v>
+        <v>1589</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/data/Pick_Calibration.xlsx
+++ b/data/Pick_Calibration.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-23 ~ 2026-08-28</t>
+          <t>2026-07-23 ~ 2026-08-29</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5,109건</t>
+          <t>5,339건</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>995건</t>
+          <t>1,039건</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.2323</t>
+          <t>0.2322</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.8%</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.4%</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-4.1% ~ +1.9%</t>
+          <t>-4.3% ~ +1.5%</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.8%</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-7.0%</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-9.7% ~ -3.7%</t>
+          <t>-9.9% ~ -4.1%</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>761</v>
+        <v>793</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -725,16 +725,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+2.0%</t>
+          <t>+1.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="3">
@@ -744,16 +744,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1428</v>
+        <v>1496</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1197</v>
+        <v>1249</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="5">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>969</v>
+        <v>1014</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -809,12 +809,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -837,12 +837,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>73.2%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1715</v>
+        <v>1793</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -949,12 +949,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.3%</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1177</v>
+        <v>1229</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1150</v>
+        <v>1202</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1029,17 +1029,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>49.8%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-0.0%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>49.7%</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>-0.0%</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>49.6%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1067</v>
+        <v>1115</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3306</v>
+        <v>3437</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.2315</v>
+        <v>0.2314</v>
       </c>
     </row>
     <row r="3">
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1589</v>
+        <v>1688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.2338</v>
+        <v>0.2337</v>
       </c>
     </row>
     <row r="4">

--- a/data/Pick_Calibration.xlsx
+++ b/data/Pick_Calibration.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-23 ~ 2026-08-29</t>
+          <t>2026-07-23 ~ 2026-08-30</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5,339건</t>
+          <t>5,470건</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1,039건</t>
+          <t>1,054건</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.2322</t>
+          <t>0.2318</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>39.1%</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-1.1%</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-4.3% ~ +1.5%</t>
+          <t>-4.0% ~ +1.8%</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-6.7%</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-9.9% ~ -4.1%</t>
+          <t>-9.6% ~ -3.8%</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>793</v>
+        <v>816</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -725,12 +725,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+1.8%</t>
+          <t>+1.6%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1496</v>
+        <v>1531</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>+1.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -772,21 +772,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1249</v>
+        <v>1280</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>+0.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1014</v>
+        <v>1035</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -809,12 +809,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -828,25 +828,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="7">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -865,16 +865,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>73.2%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1793</v>
+        <v>1838</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1229</v>
+        <v>1259</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.0%</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1202</v>
+        <v>1232</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1115</v>
+        <v>1141</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1146,11 +1146,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3437</v>
+        <v>3568</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.2314</v>
+        <v>0.2307</v>
       </c>
     </row>
     <row r="3">

--- a/data/Pick_Calibration.xlsx
+++ b/data/Pick_Calibration.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-23 ~ 2026-08-30</t>
+          <t>2026-07-23 ~ 2026-09-03</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5,470건</t>
+          <t>6,216건</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1,054건</t>
+          <t>1,161건</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.2318</t>
+          <t>0.2331</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.2%</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>39.9%</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.7%</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-4.0% ~ +1.8%</t>
+          <t>-4.4% ~ +1.0%</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-7.3%</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-9.6% ~ -3.8%</t>
+          <t>-9.9% ~ -4.6%</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>816</v>
+        <v>936</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -725,12 +725,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+1.6%</t>
+          <t>+2.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1531</v>
+        <v>1723</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -753,12 +753,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+1.3%</t>
+          <t>+1.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1280</v>
+        <v>1459</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -781,12 +781,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+0.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1035</v>
+        <v>1181</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -809,12 +809,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>469</v>
+        <v>537</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -837,16 +837,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="7">
@@ -856,25 +856,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>339</v>
+        <v>380</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1838</v>
+        <v>2090</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -980,11 +980,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1259</v>
+        <v>1427</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1232</v>
+        <v>1400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1060,11 +1060,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1141</v>
+        <v>1299</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-7.0%</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3568</v>
+        <v>4053</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.2307</v>
+        <v>0.2322</v>
       </c>
     </row>
     <row r="3">
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1688</v>
+        <v>1949</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1188,11 +1188,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.2337</v>
+        <v>0.2349</v>
       </c>
     </row>
     <row r="4">

--- a/data/Pick_Calibration.xlsx
+++ b/data/Pick_Calibration.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-23 ~ 2026-09-03</t>
+          <t>2026-07-23 ~ 2026-09-04</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6,216건</t>
+          <t>6,351건</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1,161건</t>
+          <t>1,188건</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.2331</t>
+          <t>0.2334</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>38.0%</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-1.8%</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-4.4% ~ +1.0%</t>
+          <t>-4.5% ~ +0.8%</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.4%</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-9.9% ~ -4.6%</t>
+          <t>-10.1% ~ -4.8%</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>936</v>
+        <v>951</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -725,12 +725,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>+2.7%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1723</v>
+        <v>1770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+1.5%</t>
+          <t>+1.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1459</v>
+        <v>1485</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -781,12 +781,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1181</v>
+        <v>1207</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -809,12 +809,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -837,12 +837,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2090</v>
+        <v>2135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1427</v>
+        <v>1457</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1400</v>
+        <v>1430</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1299</v>
+        <v>1329</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4053</v>
+        <v>4134</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1949</v>
+        <v>2003</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1188,11 +1188,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.2349</v>
+        <v>0.2357</v>
       </c>
     </row>
     <row r="4">
